--- a/grex/extraxted_rules/rules_obj_bw_v_aux.xlsx
+++ b/grex/extraxted_rules/rules_obj_bw_v_aux.xlsx
@@ -1,30 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaal882/Documents/Courses/SDTB_project/grex/rules_results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaal882/Documents/GitHub/Diachronic_Treebanks_DigPhil/grex/extraxted_rules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A6E2C11-6391-F149-A2E6-1DB4A61F17C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B300B372-FC13-1840-8F8E-81F85ADED87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="2460" windowWidth="27240" windowHeight="16180" xr2:uid="{FB57832D-4CEF-9C42-AD43-D8205A349FF3}"/>
+    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{FB57832D-4CEF-9C42-AD43-D8205A349FF3}"/>
   </bookViews>
   <sheets>
     <sheet name="rules_item_bw_v_aux_1" sheetId="1" r:id="rId1"/>
     <sheet name="sent_by_conclusion" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">rules_item_bw_v_aux_1!$A$8:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$12:$A$492</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="221">
   <si>
     <t>Scope</t>
   </si>
@@ -150,13 +164,656 @@
   </si>
   <si>
     <t>Grammatical phenomenon: object between a verb and its auxiliary</t>
+  </si>
+  <si>
+    <t>Treebank</t>
+  </si>
+  <si>
+    <t>Sentences</t>
+  </si>
+  <si>
+    <t>Sw_Tal 1970s</t>
+  </si>
+  <si>
+    <t>6,038 </t>
+  </si>
+  <si>
+    <t>Sw_LinES</t>
+  </si>
+  <si>
+    <t>5,696 </t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>DigPhil DiachronicTreebank Evaluation</t>
+  </si>
+  <si>
+    <t>DigPhil DiachronicTreebank Evaluation </t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Blind annotation</t>
+  </si>
+  <si>
+    <t>Project created by: </t>
+  </si>
+  <si>
+    <t>alanev52</t>
+  </si>
+  <si>
+    <t>Project statistics</t>
+  </si>
+  <si>
+    <t>Select sample, keep it empty if you want to select all samples</t>
+  </si>
+  <si>
+    <t>recent trees</t>
+  </si>
+  <si>
+    <t>Search in</t>
+  </si>
+  <si>
+    <t>% Search for a token of a given upos</t>
+  </si>
+  <si>
+    <t>% Available tags: ADJ, ADP, ADV, AUX, CONJ, DET, INTJ, NOUN, NUM, PART, PRON, PROPN, PUNCT, SCONJ, SYM, VERB, X</t>
+  </si>
+  <si>
+    <r>
+      <t>pattern</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t xml:space="preserve"> { V [upos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF009900"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>VERB]; A [upos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF009900"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>AUX|VERB]; V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF009900"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>-[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>aux</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF009900"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>]-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>A; X [upos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF009900"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>NOUN|PNOUN]; V [VerbForm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF009900"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>Inf];  V &gt; X; X &gt; A}</t>
+    </r>
+  </si>
+  <si>
+    <t>158 occurrences in 157 sentences (for 2 users)</t>
+  </si>
+  <si>
+    <t>996_letter141673</t>
+  </si>
+  <si>
+    <t>   </t>
+  </si>
+  <si>
+    <t>859_sec192</t>
+  </si>
+  <si>
+    <t>856_sec25</t>
+  </si>
+  <si>
+    <t>714_letter141673</t>
+  </si>
+  <si>
+    <t>565_letter141673</t>
+  </si>
+  <si>
+    <t>506_letter141673</t>
+  </si>
+  <si>
+    <t>501_sec192</t>
+  </si>
+  <si>
+    <t>4_letter141673</t>
+  </si>
+  <si>
+    <t>468_letter141673</t>
+  </si>
+  <si>
+    <t>447_letter141673</t>
+  </si>
+  <si>
+    <t>381_sec330</t>
+  </si>
+  <si>
+    <t>338_sec25</t>
+  </si>
+  <si>
+    <t>2521_letter141673</t>
+  </si>
+  <si>
+    <t>2514_letter141673</t>
+  </si>
+  <si>
+    <t>2461_letter141673</t>
+  </si>
+  <si>
+    <t>228_letter141673</t>
+  </si>
+  <si>
+    <t>2258_letter141673</t>
+  </si>
+  <si>
+    <t>2046_sec192</t>
+  </si>
+  <si>
+    <t>1937_letter141673</t>
+  </si>
+  <si>
+    <t>1916_letter141673</t>
+  </si>
+  <si>
+    <t>1914_sec192</t>
+  </si>
+  <si>
+    <t>1903_letter141673</t>
+  </si>
+  <si>
+    <t>1819_letter141673</t>
+  </si>
+  <si>
+    <t>1701_sec330</t>
+  </si>
+  <si>
+    <t>1607_sec330</t>
+  </si>
+  <si>
+    <t>1513_sec330</t>
+  </si>
+  <si>
+    <t>1483_sec330</t>
+  </si>
+  <si>
+    <t>1436_sec192</t>
+  </si>
+  <si>
+    <t>1423_sec330</t>
+  </si>
+  <si>
+    <t>1422_sec330</t>
+  </si>
+  <si>
+    <t>1382_sec330</t>
+  </si>
+  <si>
+    <t>1175_sec330</t>
+  </si>
+  <si>
+    <t>110_letter141673</t>
+  </si>
+  <si>
+    <t>101_letter141673</t>
+  </si>
+  <si>
+    <t>994_sec839</t>
+  </si>
+  <si>
+    <t>84_letter141677</t>
+  </si>
+  <si>
+    <t>841_sec839</t>
+  </si>
+  <si>
+    <t>821_letter141677</t>
+  </si>
+  <si>
+    <t>76_letter141677</t>
+  </si>
+  <si>
+    <t>701_sec839</t>
+  </si>
+  <si>
+    <t>620_sec268</t>
+  </si>
+  <si>
+    <t>506_sec839</t>
+  </si>
+  <si>
+    <t>4722_letter141677</t>
+  </si>
+  <si>
+    <t>45_letter141677</t>
+  </si>
+  <si>
+    <t>4471_letter141677</t>
+  </si>
+  <si>
+    <t>378_sec839</t>
+  </si>
+  <si>
+    <t>359_sec267</t>
+  </si>
+  <si>
+    <t>3264_letter141677</t>
+  </si>
+  <si>
+    <t>3245_letter141677</t>
+  </si>
+  <si>
+    <t>3199_letter141677</t>
+  </si>
+  <si>
+    <t>3086_letter141677</t>
+  </si>
+  <si>
+    <t>2947_letter141677</t>
+  </si>
+  <si>
+    <t>2695_letter141677</t>
+  </si>
+  <si>
+    <t>2688_letter141677</t>
+  </si>
+  <si>
+    <t>2620_sec268</t>
+  </si>
+  <si>
+    <t>2602_letter141677</t>
+  </si>
+  <si>
+    <t>259_letter141677</t>
+  </si>
+  <si>
+    <t>2586_letter141677</t>
+  </si>
+  <si>
+    <t>2550_sec268</t>
+  </si>
+  <si>
+    <t>2537_letter141677</t>
+  </si>
+  <si>
+    <t>2514_letter141677</t>
+  </si>
+  <si>
+    <t>2491_letter141677</t>
+  </si>
+  <si>
+    <t>2443_letter141677</t>
+  </si>
+  <si>
+    <t>2351_letter141677</t>
+  </si>
+  <si>
+    <t>2331_letter141677</t>
+  </si>
+  <si>
+    <t>2241_letter141677</t>
+  </si>
+  <si>
+    <t>2210_letter141677</t>
+  </si>
+  <si>
+    <t>216_letter141677</t>
+  </si>
+  <si>
+    <t>2084_letter141677</t>
+  </si>
+  <si>
+    <t>2028_letter141677</t>
+  </si>
+  <si>
+    <t>1854_sec268</t>
+  </si>
+  <si>
+    <t>1851_sec267</t>
+  </si>
+  <si>
+    <t>1744_sec267</t>
+  </si>
+  <si>
+    <t>1664_sec267</t>
+  </si>
+  <si>
+    <t>1640_letter141677</t>
+  </si>
+  <si>
+    <t>1413_letter141677</t>
+  </si>
+  <si>
+    <t>135_letter141677</t>
+  </si>
+  <si>
+    <t>134_sec268</t>
+  </si>
+  <si>
+    <t>1192_letter141677</t>
+  </si>
+  <si>
+    <t>1099_sec267</t>
+  </si>
+  <si>
+    <t>1091_sec839</t>
+  </si>
+  <si>
+    <t>1028_sec839</t>
+  </si>
+  <si>
+    <t>93_sec254</t>
+  </si>
+  <si>
+    <t>779_sec494</t>
+  </si>
+  <si>
+    <t>733_sec494</t>
+  </si>
+  <si>
+    <t>648_sec494</t>
+  </si>
+  <si>
+    <t>621_sec545</t>
+  </si>
+  <si>
+    <t>620_sec545</t>
+  </si>
+  <si>
+    <t>5390_sec545</t>
+  </si>
+  <si>
+    <t>5352_sec545</t>
+  </si>
+  <si>
+    <t>5131_sec545</t>
+  </si>
+  <si>
+    <t>507_sec324</t>
+  </si>
+  <si>
+    <t>464_sec324</t>
+  </si>
+  <si>
+    <t>459_sec988</t>
+  </si>
+  <si>
+    <t>445_sec494</t>
+  </si>
+  <si>
+    <t>402_sec988</t>
+  </si>
+  <si>
+    <t>3450_sec545</t>
+  </si>
+  <si>
+    <t>3446_sec545</t>
+  </si>
+  <si>
+    <t>3330_sec545</t>
+  </si>
+  <si>
+    <t>3166_sec545</t>
+  </si>
+  <si>
+    <t>2687_sec545</t>
+  </si>
+  <si>
+    <t>23_sec254</t>
+  </si>
+  <si>
+    <t>2019_sec545</t>
+  </si>
+  <si>
+    <t>15_sec991</t>
+  </si>
+  <si>
+    <t>1070_sec252</t>
+  </si>
+  <si>
+    <t>75_sec1102</t>
+  </si>
+  <si>
+    <t>755_sec306</t>
+  </si>
+  <si>
+    <t>754_sec306</t>
+  </si>
+  <si>
+    <t>753_sec306</t>
+  </si>
+  <si>
+    <t>691_sec1102</t>
+  </si>
+  <si>
+    <t>668_sec1031</t>
+  </si>
+  <si>
+    <t>667_sec1063</t>
+  </si>
+  <si>
+    <t>655_sec1031</t>
+  </si>
+  <si>
+    <t>64_sec486</t>
+  </si>
+  <si>
+    <t>648_sec1031</t>
+  </si>
+  <si>
+    <t>643_sec339</t>
+  </si>
+  <si>
+    <t>560_sec1063</t>
+  </si>
+  <si>
+    <t>556_sec452</t>
+  </si>
+  <si>
+    <t>512_sec1102</t>
+  </si>
+  <si>
+    <t>4_sec452</t>
+  </si>
+  <si>
+    <t>495_sec1108</t>
+  </si>
+  <si>
+    <t>463_sec486</t>
+  </si>
+  <si>
+    <t>459_sec885</t>
+  </si>
+  <si>
+    <t>342_sec415</t>
+  </si>
+  <si>
+    <t>327_sec306</t>
+  </si>
+  <si>
+    <t>289_sec492</t>
+  </si>
+  <si>
+    <t>200_sec519</t>
+  </si>
+  <si>
+    <t>199_sec519</t>
+  </si>
+  <si>
+    <t>197_sec519</t>
+  </si>
+  <si>
+    <t>18_sec519</t>
+  </si>
+  <si>
+    <t>144_sec339</t>
+  </si>
+  <si>
+    <t>103_sec1108</t>
+  </si>
+  <si>
+    <t>82_sec609</t>
+  </si>
+  <si>
+    <t>763_sec613</t>
+  </si>
+  <si>
+    <t>762_sec613</t>
+  </si>
+  <si>
+    <t>63_sec631</t>
+  </si>
+  <si>
+    <t>563_sec631</t>
+  </si>
+  <si>
+    <t>505_sec397</t>
+  </si>
+  <si>
+    <t>439_sec613</t>
+  </si>
+  <si>
+    <t>42_sec397</t>
+  </si>
+  <si>
+    <t>376_sec397</t>
+  </si>
+  <si>
+    <t>301_sec631</t>
+  </si>
+  <si>
+    <t>298_sec397</t>
+  </si>
+  <si>
+    <t>251_sec609</t>
+  </si>
+  <si>
+    <t>2306_sec609</t>
+  </si>
+  <si>
+    <t>2227_sec609</t>
+  </si>
+  <si>
+    <t>2198_sec609</t>
+  </si>
+  <si>
+    <t>2060_sec609</t>
+  </si>
+  <si>
+    <t>1859_sec609</t>
+  </si>
+  <si>
+    <t>1502_sec1033</t>
+  </si>
+  <si>
+    <t>1451_sec609</t>
+  </si>
+  <si>
+    <t>1291_sec609</t>
+  </si>
+  <si>
+    <t>1211_sec609</t>
+  </si>
+  <si>
+    <t>1195_sec609</t>
+  </si>
+  <si>
+    <t>1700_1749_714_letter141673</t>
+  </si>
+  <si>
+    <t>1700_1749_338_sec25</t>
+  </si>
+  <si>
+    <t>1700_1749_1382_sec330</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="39">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -295,6 +952,126 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val=".AppleSystemUIFont"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val=".AppleSystemUIFont"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF4A2769"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF689F38"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF4A2769"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF15A700"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF4A2769"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF999999"/>
+      <name val="Courier"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFAA5500"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3300AA"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF009900"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF9E9E9E"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -630,7 +1407,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -673,18 +1450,37 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -718,6 +1514,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1038,37 +1835,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F18D64-2088-AA49-8C64-F0C83DA9E19B}">
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="56.33203125" customWidth="1"/>
+    <col min="11" max="11" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1084,7 +1882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1107,7 +1905,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1122,7 +1920,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="17">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1150,8 +1948,20 @@
       <c r="I8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="17">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1989,20 @@
       <c r="I9" s="2">
         <v>1.722</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="6">
+        <v>45</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="17">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -1208,8 +2030,20 @@
       <c r="I10" s="2">
         <v>1.2789999999999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="K10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="6">
+        <v>8</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1238,7 +2072,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -1267,7 +2101,7 @@
         <v>0.433</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
@@ -1296,7 +2130,7 @@
         <v>0.29599999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1325,7 +2159,7 @@
         <v>0.248</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
@@ -1354,7 +2188,7 @@
         <v>0.24199999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -1383,7 +2217,7 @@
         <v>0.21099999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
@@ -1412,7 +2246,7 @@
         <v>0.20100000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
@@ -1441,7 +2275,7 @@
         <v>0.18099999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1470,7 +2304,7 @@
         <v>0.127</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
@@ -1499,7 +2333,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
@@ -1528,7 +2362,7 @@
         <v>0.16200000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22" s="3" t="s">
         <v>31</v>
       </c>
@@ -1557,7 +2391,7 @@
         <v>0.16200000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23" s="3" t="s">
         <v>32</v>
       </c>
@@ -1598,17 +2432,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC52DD7-8C6C-D54B-AAC0-42D332EEAC76}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1616,4 +2450,2630 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0571EE6E-6C04-5D45-AB83-7BA3F9B01D2E}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:A492"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="20">
+      <c r="A1" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="18">
+      <c r="A3" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="18">
+      <c r="A6" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="18">
+      <c r="A8" s="15"/>
+    </row>
+    <row r="10" spans="1:1" ht="18">
+      <c r="A10" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="18">
+      <c r="A12" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="18" hidden="1">
+      <c r="A13" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="18" hidden="1">
+      <c r="A14" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="19" hidden="1">
+      <c r="A15" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" hidden="1">
+      <c r="A16" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="19" hidden="1">
+      <c r="A17" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" hidden="1">
+      <c r="A18" s="18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="19" hidden="1">
+      <c r="A19" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" hidden="1">
+      <c r="A20" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="20" hidden="1">
+      <c r="A21" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="23" hidden="1">
+      <c r="A22" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="20">
+      <c r="A23" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="23" hidden="1">
+      <c r="A24" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="23" hidden="1">
+      <c r="A25" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="20">
+      <c r="A26" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="23" hidden="1">
+      <c r="A27" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="23" hidden="1">
+      <c r="A28" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="20">
+      <c r="A29" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="23" hidden="1">
+      <c r="A30" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="23" hidden="1">
+      <c r="A31" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="20">
+      <c r="A32" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="23" hidden="1">
+      <c r="A33" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="23" hidden="1">
+      <c r="A34" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="20">
+      <c r="A35" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="23" hidden="1">
+      <c r="A36" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="23" hidden="1">
+      <c r="A37" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="20">
+      <c r="A38" s="22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="23" hidden="1">
+      <c r="A39" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="23" hidden="1">
+      <c r="A40" s="21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="20">
+      <c r="A41" s="22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="23" hidden="1">
+      <c r="A42" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="23" hidden="1">
+      <c r="A43" s="21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="20">
+      <c r="A44" s="22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="23" hidden="1">
+      <c r="A45" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="23" hidden="1">
+      <c r="A46" s="21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="20">
+      <c r="A47" s="22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="23" hidden="1">
+      <c r="A48" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="23" hidden="1">
+      <c r="A49" s="21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="20">
+      <c r="A50" s="22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="23" hidden="1">
+      <c r="A51" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="23" hidden="1">
+      <c r="A52" s="21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="20">
+      <c r="A53" s="22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="23" hidden="1">
+      <c r="A54" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="23" hidden="1">
+      <c r="A55" s="21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="20">
+      <c r="A56" s="22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="23" hidden="1">
+      <c r="A57" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="23" hidden="1">
+      <c r="A58" s="21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="20">
+      <c r="A59" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="23" hidden="1">
+      <c r="A60" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="23" hidden="1">
+      <c r="A61" s="21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="20">
+      <c r="A62" s="22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="23" hidden="1">
+      <c r="A63" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="23" hidden="1">
+      <c r="A64" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="20">
+      <c r="A65" s="22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="23" hidden="1">
+      <c r="A66" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="23" hidden="1">
+      <c r="A67" s="21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="20">
+      <c r="A68" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="23" hidden="1">
+      <c r="A69" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="23" hidden="1">
+      <c r="A70" s="21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="20">
+      <c r="A71" s="22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="23" hidden="1">
+      <c r="A72" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="23" hidden="1">
+      <c r="A73" s="21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="20">
+      <c r="A74" s="22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="23" hidden="1">
+      <c r="A75" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="23" hidden="1">
+      <c r="A76" s="21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="20">
+      <c r="A77" s="22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="23" hidden="1">
+      <c r="A78" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="23" hidden="1">
+      <c r="A79" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="20">
+      <c r="A80" s="22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="23" hidden="1">
+      <c r="A81" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="23" hidden="1">
+      <c r="A82" s="21">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="20">
+      <c r="A83" s="22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="23" hidden="1">
+      <c r="A84" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="23" hidden="1">
+      <c r="A85" s="21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="20">
+      <c r="A86" s="22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="23" hidden="1">
+      <c r="A87" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="23" hidden="1">
+      <c r="A88" s="21">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="20">
+      <c r="A89" s="22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="23" hidden="1">
+      <c r="A90" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="23" hidden="1">
+      <c r="A91" s="21">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="20">
+      <c r="A92" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="23" hidden="1">
+      <c r="A93" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="23" hidden="1">
+      <c r="A94" s="21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="20">
+      <c r="A95" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="23" hidden="1">
+      <c r="A96" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="23" hidden="1">
+      <c r="A97" s="21">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="20">
+      <c r="A98" s="22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="23" hidden="1">
+      <c r="A99" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="23" hidden="1">
+      <c r="A100" s="21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="20">
+      <c r="A101" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="23" hidden="1">
+      <c r="A102" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="23" hidden="1">
+      <c r="A103" s="21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="20">
+      <c r="A104" s="22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="23" hidden="1">
+      <c r="A105" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="23" hidden="1">
+      <c r="A106" s="21">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="20">
+      <c r="A107" s="22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="23" hidden="1">
+      <c r="A108" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="23" hidden="1">
+      <c r="A109" s="21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="20">
+      <c r="A110" s="22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="23" hidden="1">
+      <c r="A111" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="23" hidden="1">
+      <c r="A112" s="21">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="20">
+      <c r="A113" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="23" hidden="1">
+      <c r="A114" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="23" hidden="1">
+      <c r="A115" s="21">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="20">
+      <c r="A116" s="22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="23" hidden="1">
+      <c r="A117" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="23" hidden="1">
+      <c r="A118" s="21">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="20">
+      <c r="A119" s="22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="23" hidden="1">
+      <c r="A120" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="23" hidden="1">
+      <c r="A121" s="21">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="20">
+      <c r="A122" s="22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="23" hidden="1">
+      <c r="A123" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="23" hidden="1">
+      <c r="A124" s="21">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="20">
+      <c r="A125" s="22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="23" hidden="1">
+      <c r="A126" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="23" hidden="1">
+      <c r="A127" s="21">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="20">
+      <c r="A128" s="22" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="23" hidden="1">
+      <c r="A129" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="23" hidden="1">
+      <c r="A130" s="21">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="20">
+      <c r="A131" s="22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="23" hidden="1">
+      <c r="A132" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="23" hidden="1">
+      <c r="A133" s="21">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="20">
+      <c r="A134" s="22" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="23" hidden="1">
+      <c r="A135" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="23" hidden="1">
+      <c r="A136" s="21">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="20">
+      <c r="A137" s="22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="23" hidden="1">
+      <c r="A138" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="23" hidden="1">
+      <c r="A139" s="21">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="20">
+      <c r="A140" s="22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="23" hidden="1">
+      <c r="A141" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="23" hidden="1">
+      <c r="A142" s="21">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="20">
+      <c r="A143" s="22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="23" hidden="1">
+      <c r="A144" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="23" hidden="1">
+      <c r="A145" s="21">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="20">
+      <c r="A146" s="22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="23" hidden="1">
+      <c r="A147" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="23" hidden="1">
+      <c r="A148" s="21">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="20">
+      <c r="A149" s="22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="23" hidden="1">
+      <c r="A150" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="23" hidden="1">
+      <c r="A151" s="21">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="20">
+      <c r="A152" s="22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="23" hidden="1">
+      <c r="A153" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="23" hidden="1">
+      <c r="A154" s="21">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="20">
+      <c r="A155" s="22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="23" hidden="1">
+      <c r="A156" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="23" hidden="1">
+      <c r="A157" s="21">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="20">
+      <c r="A158" s="22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="23" hidden="1">
+      <c r="A159" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="23" hidden="1">
+      <c r="A160" s="21">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="20">
+      <c r="A161" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="23" hidden="1">
+      <c r="A162" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="23" hidden="1">
+      <c r="A163" s="21">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="20">
+      <c r="A164" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="23" hidden="1">
+      <c r="A165" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="23" hidden="1">
+      <c r="A166" s="21">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="20">
+      <c r="A167" s="22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="23" hidden="1">
+      <c r="A168" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="23" hidden="1">
+      <c r="A169" s="21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="20">
+      <c r="A170" s="22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="23" hidden="1">
+      <c r="A171" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="23" hidden="1">
+      <c r="A172" s="21">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="20">
+      <c r="A173" s="22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="23" hidden="1">
+      <c r="A174" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="23" hidden="1">
+      <c r="A175" s="21">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="20">
+      <c r="A176" s="22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="23" hidden="1">
+      <c r="A177" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="23" hidden="1">
+      <c r="A178" s="21">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="20">
+      <c r="A179" s="22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="23" hidden="1">
+      <c r="A180" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="23" hidden="1">
+      <c r="A181" s="21">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="20">
+      <c r="A182" s="22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="23" hidden="1">
+      <c r="A183" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="23" hidden="1">
+      <c r="A184" s="21">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="20">
+      <c r="A185" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="23" hidden="1">
+      <c r="A186" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="23" hidden="1">
+      <c r="A187" s="21">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="20">
+      <c r="A188" s="22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="23" hidden="1">
+      <c r="A189" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="23" hidden="1">
+      <c r="A190" s="21">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="20">
+      <c r="A191" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="23" hidden="1">
+      <c r="A192" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="23" hidden="1">
+      <c r="A193" s="21">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="20">
+      <c r="A194" s="22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="23" hidden="1">
+      <c r="A195" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="23" hidden="1">
+      <c r="A196" s="21">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="20">
+      <c r="A197" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="23" hidden="1">
+      <c r="A198" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="23" hidden="1">
+      <c r="A199" s="21">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="20">
+      <c r="A200" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="23" hidden="1">
+      <c r="A201" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" ht="23" hidden="1">
+      <c r="A202" s="21">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" ht="20">
+      <c r="A203" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" ht="23" hidden="1">
+      <c r="A204" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" ht="23" hidden="1">
+      <c r="A205" s="21">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" ht="20">
+      <c r="A206" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" ht="23" hidden="1">
+      <c r="A207" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" ht="23" hidden="1">
+      <c r="A208" s="21">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" ht="20">
+      <c r="A209" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" ht="23" hidden="1">
+      <c r="A210" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" ht="23" hidden="1">
+      <c r="A211" s="21">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" ht="20">
+      <c r="A212" s="22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" ht="23" hidden="1">
+      <c r="A213" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" ht="23" hidden="1">
+      <c r="A214" s="21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" ht="20">
+      <c r="A215" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" ht="23" hidden="1">
+      <c r="A216" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" ht="23" hidden="1">
+      <c r="A217" s="21">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" ht="20">
+      <c r="A218" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" ht="23" hidden="1">
+      <c r="A219" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" ht="23" hidden="1">
+      <c r="A220" s="21">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" ht="20">
+      <c r="A221" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" ht="23" hidden="1">
+      <c r="A222" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" ht="23" hidden="1">
+      <c r="A223" s="21">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" ht="20">
+      <c r="A224" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" ht="23" hidden="1">
+      <c r="A225" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" ht="23" hidden="1">
+      <c r="A226" s="21">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" ht="20">
+      <c r="A227" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" ht="23" hidden="1">
+      <c r="A228" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" ht="23" hidden="1">
+      <c r="A229" s="21">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" ht="20">
+      <c r="A230" s="22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" ht="23" hidden="1">
+      <c r="A231" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" ht="23" hidden="1">
+      <c r="A232" s="21">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" ht="20">
+      <c r="A233" s="22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" ht="23" hidden="1">
+      <c r="A234" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" ht="23" hidden="1">
+      <c r="A235" s="21">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" ht="20">
+      <c r="A236" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" ht="23" hidden="1">
+      <c r="A237" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" ht="23" hidden="1">
+      <c r="A238" s="21">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" ht="20">
+      <c r="A239" s="22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" ht="23" hidden="1">
+      <c r="A240" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" ht="23" hidden="1">
+      <c r="A241" s="21">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" ht="20">
+      <c r="A242" s="22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" ht="23" hidden="1">
+      <c r="A243" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" ht="23" hidden="1">
+      <c r="A244" s="21">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" ht="20">
+      <c r="A245" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" ht="23" hidden="1">
+      <c r="A246" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" ht="23" hidden="1">
+      <c r="A247" s="21">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" ht="20">
+      <c r="A248" s="22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" ht="23" hidden="1">
+      <c r="A249" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" ht="23" hidden="1">
+      <c r="A250" s="21">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" ht="20">
+      <c r="A251" s="22" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" ht="23" hidden="1">
+      <c r="A252" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" ht="23" hidden="1">
+      <c r="A253" s="21">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" ht="20">
+      <c r="A254" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" ht="23" hidden="1">
+      <c r="A255" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" ht="23" hidden="1">
+      <c r="A256" s="21">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" ht="20">
+      <c r="A257" s="22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" ht="23" hidden="1">
+      <c r="A258" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" ht="23" hidden="1">
+      <c r="A259" s="21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" ht="20">
+      <c r="A260" s="22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" ht="23" hidden="1">
+      <c r="A261" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" ht="23" hidden="1">
+      <c r="A262" s="21">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" ht="20">
+      <c r="A263" s="22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" ht="23" hidden="1">
+      <c r="A264" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" ht="23" hidden="1">
+      <c r="A265" s="21">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" ht="20">
+      <c r="A266" s="22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" ht="23" hidden="1">
+      <c r="A267" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" ht="23" hidden="1">
+      <c r="A268" s="21">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" ht="20">
+      <c r="A269" s="22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" ht="23" hidden="1">
+      <c r="A270" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" ht="23" hidden="1">
+      <c r="A271" s="21">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" ht="20">
+      <c r="A272" s="22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" ht="23" hidden="1">
+      <c r="A273" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" ht="23" hidden="1">
+      <c r="A274" s="21">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" ht="20">
+      <c r="A275" s="22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" ht="23" hidden="1">
+      <c r="A276" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" ht="23" hidden="1">
+      <c r="A277" s="21">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" ht="20">
+      <c r="A278" s="22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" ht="23" hidden="1">
+      <c r="A279" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" ht="23" hidden="1">
+      <c r="A280" s="21">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" ht="20">
+      <c r="A281" s="22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" ht="23" hidden="1">
+      <c r="A282" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" ht="23" hidden="1">
+      <c r="A283" s="21">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" ht="20">
+      <c r="A284" s="22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" ht="23" hidden="1">
+      <c r="A285" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" ht="23" hidden="1">
+      <c r="A286" s="21">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" ht="20">
+      <c r="A287" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" ht="23" hidden="1">
+      <c r="A288" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" ht="23" hidden="1">
+      <c r="A289" s="21">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" ht="20">
+      <c r="A290" s="22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" ht="23" hidden="1">
+      <c r="A291" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" ht="23" hidden="1">
+      <c r="A292" s="21">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" ht="20">
+      <c r="A293" s="22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" ht="23" hidden="1">
+      <c r="A294" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" ht="23" hidden="1">
+      <c r="A295" s="21">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" ht="20">
+      <c r="A296" s="22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" ht="23" hidden="1">
+      <c r="A297" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" ht="23" hidden="1">
+      <c r="A298" s="21">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" ht="20">
+      <c r="A299" s="22" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" ht="23" hidden="1">
+      <c r="A300" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" ht="23" hidden="1">
+      <c r="A301" s="21">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" ht="20">
+      <c r="A302" s="22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" ht="23" hidden="1">
+      <c r="A303" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" ht="23" hidden="1">
+      <c r="A304" s="21">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" ht="20">
+      <c r="A305" s="22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" ht="23" hidden="1">
+      <c r="A306" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" ht="23" hidden="1">
+      <c r="A307" s="21">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" ht="20">
+      <c r="A308" s="22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" ht="23" hidden="1">
+      <c r="A309" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" ht="23" hidden="1">
+      <c r="A310" s="21">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" ht="20">
+      <c r="A311" s="22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" ht="23" hidden="1">
+      <c r="A312" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" ht="23" hidden="1">
+      <c r="A313" s="21">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" ht="20">
+      <c r="A314" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" ht="23" hidden="1">
+      <c r="A315" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" ht="23" hidden="1">
+      <c r="A316" s="21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" ht="20">
+      <c r="A317" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" ht="23" hidden="1">
+      <c r="A318" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" ht="23" hidden="1">
+      <c r="A319" s="21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" ht="20">
+      <c r="A320" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" ht="23" hidden="1">
+      <c r="A321" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" ht="23" hidden="1">
+      <c r="A322" s="21">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" ht="20">
+      <c r="A323" s="22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" ht="23" hidden="1">
+      <c r="A324" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" ht="23" hidden="1">
+      <c r="A325" s="21">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" ht="20">
+      <c r="A326" s="22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" ht="23" hidden="1">
+      <c r="A327" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" ht="23" hidden="1">
+      <c r="A328" s="21">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" ht="20">
+      <c r="A329" s="22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" ht="23" hidden="1">
+      <c r="A330" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" ht="23" hidden="1">
+      <c r="A331" s="21">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" ht="20">
+      <c r="A332" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" ht="23" hidden="1">
+      <c r="A333" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" ht="23" hidden="1">
+      <c r="A334" s="21">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" ht="20">
+      <c r="A335" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" ht="23" hidden="1">
+      <c r="A336" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" ht="23" hidden="1">
+      <c r="A337" s="21">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" ht="20">
+      <c r="A338" s="22" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" ht="23" hidden="1">
+      <c r="A339" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" ht="23" hidden="1">
+      <c r="A340" s="21">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" ht="20">
+      <c r="A341" s="22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" ht="23" hidden="1">
+      <c r="A342" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" ht="23" hidden="1">
+      <c r="A343" s="21">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" ht="20">
+      <c r="A344" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" ht="23" hidden="1">
+      <c r="A345" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" ht="23" hidden="1">
+      <c r="A346" s="21">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" ht="20">
+      <c r="A347" s="22" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" ht="23" hidden="1">
+      <c r="A348" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" ht="23" hidden="1">
+      <c r="A349" s="21">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" ht="20">
+      <c r="A350" s="22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" ht="23" hidden="1">
+      <c r="A351" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" ht="23" hidden="1">
+      <c r="A352" s="21">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" ht="20">
+      <c r="A353" s="22" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" ht="23" hidden="1">
+      <c r="A354" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" ht="23" hidden="1">
+      <c r="A355" s="21">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" ht="20">
+      <c r="A356" s="22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" ht="23" hidden="1">
+      <c r="A357" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" ht="23" hidden="1">
+      <c r="A358" s="21">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" ht="20">
+      <c r="A359" s="22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" ht="23" hidden="1">
+      <c r="A360" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" ht="23" hidden="1">
+      <c r="A361" s="21">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" ht="20">
+      <c r="A362" s="22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" ht="23" hidden="1">
+      <c r="A363" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" ht="23" hidden="1">
+      <c r="A364" s="21">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" ht="20">
+      <c r="A365" s="22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" ht="23" hidden="1">
+      <c r="A366" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" ht="23" hidden="1">
+      <c r="A367" s="21">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" ht="20">
+      <c r="A368" s="22" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" ht="23" hidden="1">
+      <c r="A369" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" ht="23" hidden="1">
+      <c r="A370" s="21">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" ht="20">
+      <c r="A371" s="22" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" ht="23" hidden="1">
+      <c r="A372" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" ht="23" hidden="1">
+      <c r="A373" s="21">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" ht="20">
+      <c r="A374" s="22" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" ht="23" hidden="1">
+      <c r="A375" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" ht="23" hidden="1">
+      <c r="A376" s="21">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" ht="20">
+      <c r="A377" s="22" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" ht="23" hidden="1">
+      <c r="A378" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" ht="23" hidden="1">
+      <c r="A379" s="21">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" ht="20">
+      <c r="A380" s="22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" ht="23" hidden="1">
+      <c r="A381" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" ht="23" hidden="1">
+      <c r="A382" s="21">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" ht="20">
+      <c r="A383" s="22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" ht="23" hidden="1">
+      <c r="A384" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" ht="23" hidden="1">
+      <c r="A385" s="21">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" ht="20">
+      <c r="A386" s="22" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" ht="23" hidden="1">
+      <c r="A387" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" ht="23" hidden="1">
+      <c r="A388" s="21">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" ht="20">
+      <c r="A389" s="22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" ht="23" hidden="1">
+      <c r="A390" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" ht="23" hidden="1">
+      <c r="A391" s="21">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" ht="20">
+      <c r="A392" s="22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" ht="23" hidden="1">
+      <c r="A393" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" ht="23" hidden="1">
+      <c r="A394" s="21">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" ht="20">
+      <c r="A395" s="22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" ht="23" hidden="1">
+      <c r="A396" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" ht="23" hidden="1">
+      <c r="A397" s="21">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" ht="20">
+      <c r="A398" s="22" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" ht="23" hidden="1">
+      <c r="A399" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" ht="23" hidden="1">
+      <c r="A400" s="21">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" ht="20">
+      <c r="A401" s="22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" ht="23" hidden="1">
+      <c r="A402" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" ht="23" hidden="1">
+      <c r="A403" s="21">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" ht="20">
+      <c r="A404" s="22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" ht="23" hidden="1">
+      <c r="A405" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" ht="23" hidden="1">
+      <c r="A406" s="21">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" ht="20">
+      <c r="A407" s="22" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" ht="23" hidden="1">
+      <c r="A408" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" ht="23" hidden="1">
+      <c r="A409" s="21">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" ht="20">
+      <c r="A410" s="22" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" ht="23" hidden="1">
+      <c r="A411" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" ht="23" hidden="1">
+      <c r="A412" s="21">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" ht="20">
+      <c r="A413" s="22" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" ht="23" hidden="1">
+      <c r="A414" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" ht="23" hidden="1">
+      <c r="A415" s="21">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" ht="20">
+      <c r="A416" s="22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" ht="23" hidden="1">
+      <c r="A417" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" ht="23" hidden="1">
+      <c r="A418" s="21">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" ht="20">
+      <c r="A419" s="22" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" ht="23" hidden="1">
+      <c r="A420" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" ht="23" hidden="1">
+      <c r="A421" s="21">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" ht="20">
+      <c r="A422" s="22" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" ht="23" hidden="1">
+      <c r="A423" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" ht="23" hidden="1">
+      <c r="A424" s="21">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" ht="20">
+      <c r="A425" s="22" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" ht="23" hidden="1">
+      <c r="A426" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" ht="23" hidden="1">
+      <c r="A427" s="21">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" ht="20">
+      <c r="A428" s="22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" ht="23" hidden="1">
+      <c r="A429" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" ht="23" hidden="1">
+      <c r="A430" s="21">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" ht="20">
+      <c r="A431" s="22" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" ht="23" hidden="1">
+      <c r="A432" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" ht="23" hidden="1">
+      <c r="A433" s="21">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" ht="20">
+      <c r="A434" s="22" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" ht="23" hidden="1">
+      <c r="A435" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" ht="23" hidden="1">
+      <c r="A436" s="21">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" ht="20">
+      <c r="A437" s="22" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" ht="23" hidden="1">
+      <c r="A438" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" ht="23" hidden="1">
+      <c r="A439" s="21">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" ht="20">
+      <c r="A440" s="22" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" ht="23" hidden="1">
+      <c r="A441" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" ht="23" hidden="1">
+      <c r="A442" s="21">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" ht="20">
+      <c r="A443" s="22" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" ht="23" hidden="1">
+      <c r="A444" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" ht="23" hidden="1">
+      <c r="A445" s="21">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" ht="20">
+      <c r="A446" s="22" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" ht="23" hidden="1">
+      <c r="A447" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" ht="23" hidden="1">
+      <c r="A448" s="21">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1" ht="20">
+      <c r="A449" s="22" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1" ht="23" hidden="1">
+      <c r="A450" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1" ht="23" hidden="1">
+      <c r="A451" s="21">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1" ht="20">
+      <c r="A452" s="22" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1" ht="23" hidden="1">
+      <c r="A453" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1" ht="23" hidden="1">
+      <c r="A454" s="21">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1" ht="20">
+      <c r="A455" s="22" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1" ht="23" hidden="1">
+      <c r="A456" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1" ht="23" hidden="1">
+      <c r="A457" s="21">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1" ht="20">
+      <c r="A458" s="22" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1" ht="23" hidden="1">
+      <c r="A459" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1" ht="23" hidden="1">
+      <c r="A460" s="21">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1" ht="20">
+      <c r="A461" s="22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1" ht="23" hidden="1">
+      <c r="A462" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1" ht="23" hidden="1">
+      <c r="A463" s="21">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1" ht="20">
+      <c r="A464" s="22" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1" ht="23" hidden="1">
+      <c r="A465" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1" ht="23" hidden="1">
+      <c r="A466" s="21">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1" ht="20">
+      <c r="A467" s="22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1" ht="23" hidden="1">
+      <c r="A468" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1" ht="23" hidden="1">
+      <c r="A469" s="21">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1" ht="20">
+      <c r="A470" s="22" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1" ht="23" hidden="1">
+      <c r="A471" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1" ht="23" hidden="1">
+      <c r="A472" s="21">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1" ht="20">
+      <c r="A473" s="22" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1" ht="23" hidden="1">
+      <c r="A474" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1" ht="23" hidden="1">
+      <c r="A475" s="21">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1" ht="20">
+      <c r="A476" s="22" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1" ht="23" hidden="1">
+      <c r="A477" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1" ht="23" hidden="1">
+      <c r="A478" s="21">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1" ht="20">
+      <c r="A479" s="22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1" ht="23" hidden="1">
+      <c r="A480" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1" ht="23" hidden="1">
+      <c r="A481" s="21">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1" ht="20">
+      <c r="A482" s="22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1" ht="23" hidden="1">
+      <c r="A483" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1" ht="23" hidden="1">
+      <c r="A484" s="21">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1" ht="20">
+      <c r="A485" s="22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1" ht="23" hidden="1">
+      <c r="A486" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1" ht="23" hidden="1">
+      <c r="A487" s="21">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1" ht="20">
+      <c r="A488" s="22" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1" ht="23" hidden="1">
+      <c r="A489" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1" ht="23" hidden="1">
+      <c r="A490" s="21">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1" ht="20">
+      <c r="A491" s="22" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1" ht="23" hidden="1">
+      <c r="A492" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A12:A492" xr:uid="{0571EE6E-6C04-5D45-AB83-7BA3F9B01D2E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="101_letter141673"/>
+        <filter val="1028_sec839"/>
+        <filter val="103_sec1108"/>
+        <filter val="1070_sec252"/>
+        <filter val="1091_sec839"/>
+        <filter val="1099_sec267"/>
+        <filter val="110_letter141673"/>
+        <filter val="1175_sec330"/>
+        <filter val="1192_letter141677"/>
+        <filter val="1195_sec609"/>
+        <filter val="1211_sec609"/>
+        <filter val="1291_sec609"/>
+        <filter val="134_sec268"/>
+        <filter val="135_letter141677"/>
+        <filter val="1382_sec330"/>
+        <filter val="1413_letter141677"/>
+        <filter val="1422_sec330"/>
+        <filter val="1423_sec330"/>
+        <filter val="1436_sec192"/>
+        <filter val="144_sec339"/>
+        <filter val="1451_sec609"/>
+        <filter val="1483_sec330"/>
+        <filter val="15_sec991"/>
+        <filter val="1502_sec1033"/>
+        <filter val="1513_sec330"/>
+        <filter val="1607_sec330"/>
+        <filter val="1640_letter141677"/>
+        <filter val="1664_sec267"/>
+        <filter val="1700_1749_1382_sec330"/>
+        <filter val="1700_1749_338_sec25"/>
+        <filter val="1700_1749_714_letter141673"/>
+        <filter val="1701_sec330"/>
+        <filter val="1744_sec267"/>
+        <filter val="18_sec519"/>
+        <filter val="1819_letter141673"/>
+        <filter val="1851_sec267"/>
+        <filter val="1854_sec268"/>
+        <filter val="1859_sec609"/>
+        <filter val="1903_letter141673"/>
+        <filter val="1914_sec192"/>
+        <filter val="1916_letter141673"/>
+        <filter val="1937_letter141673"/>
+        <filter val="197_sec519"/>
+        <filter val="199_sec519"/>
+        <filter val="200_sec519"/>
+        <filter val="2019_sec545"/>
+        <filter val="2028_letter141677"/>
+        <filter val="2046_sec192"/>
+        <filter val="2060_sec609"/>
+        <filter val="2084_letter141677"/>
+        <filter val="216_letter141677"/>
+        <filter val="2198_sec609"/>
+        <filter val="2210_letter141677"/>
+        <filter val="2227_sec609"/>
+        <filter val="2241_letter141677"/>
+        <filter val="2258_letter141673"/>
+        <filter val="228_letter141673"/>
+        <filter val="23_sec254"/>
+        <filter val="2306_sec609"/>
+        <filter val="2331_letter141677"/>
+        <filter val="2351_letter141677"/>
+        <filter val="2443_letter141677"/>
+        <filter val="2461_letter141673"/>
+        <filter val="2491_letter141677"/>
+        <filter val="251_sec609"/>
+        <filter val="2514_letter141673"/>
+        <filter val="2514_letter141677"/>
+        <filter val="2521_letter141673"/>
+        <filter val="2537_letter141677"/>
+        <filter val="2550_sec268"/>
+        <filter val="2586_letter141677"/>
+        <filter val="259_letter141677"/>
+        <filter val="2602_letter141677"/>
+        <filter val="2620_sec268"/>
+        <filter val="2687_sec545"/>
+        <filter val="2688_letter141677"/>
+        <filter val="2695_letter141677"/>
+        <filter val="289_sec492"/>
+        <filter val="2947_letter141677"/>
+        <filter val="298_sec397"/>
+        <filter val="301_sec631"/>
+        <filter val="3086_letter141677"/>
+        <filter val="3166_sec545"/>
+        <filter val="3199_letter141677"/>
+        <filter val="3245_letter141677"/>
+        <filter val="3264_letter141677"/>
+        <filter val="327_sec306"/>
+        <filter val="3330_sec545"/>
+        <filter val="338_sec25"/>
+        <filter val="342_sec415"/>
+        <filter val="3446_sec545"/>
+        <filter val="3450_sec545"/>
+        <filter val="359_sec267"/>
+        <filter val="376_sec397"/>
+        <filter val="378_sec839"/>
+        <filter val="381_sec330"/>
+        <filter val="4_letter141673"/>
+        <filter val="4_sec452"/>
+        <filter val="402_sec988"/>
+        <filter val="42_sec397"/>
+        <filter val="439_sec613"/>
+        <filter val="445_sec494"/>
+        <filter val="447_letter141673"/>
+        <filter val="4471_letter141677"/>
+        <filter val="45_letter141677"/>
+        <filter val="459_sec885"/>
+        <filter val="459_sec988"/>
+        <filter val="463_sec486"/>
+        <filter val="464_sec324"/>
+        <filter val="468_letter141673"/>
+        <filter val="4722_letter141677"/>
+        <filter val="495_sec1108"/>
+        <filter val="501_sec192"/>
+        <filter val="505_sec397"/>
+        <filter val="506_letter141673"/>
+        <filter val="506_sec839"/>
+        <filter val="507_sec324"/>
+        <filter val="512_sec1102"/>
+        <filter val="5131_sec545"/>
+        <filter val="5352_sec545"/>
+        <filter val="5390_sec545"/>
+        <filter val="556_sec452"/>
+        <filter val="560_sec1063"/>
+        <filter val="563_sec631"/>
+        <filter val="565_letter141673"/>
+        <filter val="620_sec268"/>
+        <filter val="620_sec545"/>
+        <filter val="621_sec545"/>
+        <filter val="63_sec631"/>
+        <filter val="64_sec486"/>
+        <filter val="643_sec339"/>
+        <filter val="648_sec1031"/>
+        <filter val="648_sec494"/>
+        <filter val="655_sec1031"/>
+        <filter val="667_sec1063"/>
+        <filter val="668_sec1031"/>
+        <filter val="691_sec1102"/>
+        <filter val="701_sec839"/>
+        <filter val="714_letter141673"/>
+        <filter val="733_sec494"/>
+        <filter val="75_sec1102"/>
+        <filter val="753_sec306"/>
+        <filter val="754_sec306"/>
+        <filter val="755_sec306"/>
+        <filter val="76_letter141677"/>
+        <filter val="762_sec613"/>
+        <filter val="763_sec613"/>
+        <filter val="779_sec494"/>
+        <filter val="82_sec609"/>
+        <filter val="821_letter141677"/>
+        <filter val="84_letter141677"/>
+        <filter val="841_sec839"/>
+        <filter val="856_sec25"/>
+        <filter val="859_sec192"/>
+        <filter val="93_sec254"/>
+        <filter val="994_sec839"/>
+        <filter val="996_letter141673"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" location="/projects/DigPhil%20DiachronicTreebank%20Evaluation" display="https://arborator.grew.fr/ - /projects/DigPhil%20DiachronicTreebank%20Evaluation" xr:uid="{2520CA4A-0E8F-794C-B919-5975DCBFAE63}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>